--- a/Result/profitability/3693.xlsx
+++ b/Result/profitability/3693.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.02</v>
       </c>
       <c r="M2" t="n">
-        <v>4.17375</v>
+        <v>3.74625</v>
       </c>
       <c r="N2" t="n">
-        <v>29.6675</v>
+        <v>28.88125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>3.72</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3225</v>
+        <v>3.61125</v>
       </c>
       <c r="N3" t="n">
-        <v>29.99875</v>
+        <v>29.72625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7675</v>
+        <v>2.6025</v>
       </c>
       <c r="N4" t="n">
-        <v>30.6675</v>
+        <v>30.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.77125</v>
+        <v>2.62125</v>
       </c>
       <c r="N5" t="n">
-        <v>31.4875</v>
+        <v>31.44875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>1.7675</v>
+        <v>2.08375</v>
       </c>
       <c r="N6" t="n">
-        <v>32.1</v>
+        <v>32.30875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2475</v>
+        <v>1.86375</v>
       </c>
       <c r="N7" t="n">
-        <v>32.48999999999999</v>
+        <v>32.34625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8810,6 +8810,133 @@
       </c>
       <c r="AM66" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2539</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1829</v>
+      </c>
+      <c r="E67" t="n">
+        <v>710</v>
+      </c>
+      <c r="F67" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="G67" t="n">
+        <v>373</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>14.67%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>16</v>
+      </c>
+      <c r="J67" t="n">
+        <v>389</v>
+      </c>
+      <c r="K67" t="n">
+        <v>306</v>
+      </c>
+      <c r="L67" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="M67" t="n">
+        <v>4.935</v>
+      </c>
+      <c r="N67" t="n">
+        <v>28.72625</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="X67" t="n">
+        <v>3.616883116883117</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.2045650301464255</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>21.93548387096774</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>-0.3100000000000023</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>-0.01096181046676103</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
